--- a/data/cox_xlsx/AGATE.CO.xlsx
+++ b/data/cox_xlsx/AGATE.CO.xlsx
@@ -10774,7 +10774,10 @@
         <f t="shared" si="1"/>
         <v>27.71</v>
       </c>
-      <c r="V56" s="20"/>
+      <c r="V56" s="20">
+        <f>U56</f>
+        <v>27.71</v>
+      </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">

--- a/data/cox_xlsx/AGATE.CO.xlsx
+++ b/data/cox_xlsx/AGATE.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="393">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -727,6 +727,9 @@
   </si>
   <si>
     <t>Current liabilities</t>
+  </si>
+  <si>
+    <t>Credit institutions LT</t>
   </si>
   <si>
     <t>Deferred tax liabilities</t>
@@ -11862,8 +11865,8 @@
       </c>
     </row>
     <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="14" t="s">
-        <v>221</v>
+      <c r="A80" s="19" t="s">
+        <v>236</v>
       </c>
       <c r="B80" s="15">
         <v>702.63</v>
@@ -12007,7 +12010,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
@@ -12121,7 +12124,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
@@ -12155,7 +12158,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B86" s="20"/>
       <c r="C86" s="20"/>
@@ -12187,7 +12190,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
@@ -12219,7 +12222,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B88" s="17">
         <v>714.26</v>
@@ -12287,7 +12290,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B89" s="17">
         <v>791.74</v>
@@ -12355,7 +12358,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B90" s="15">
         <v>185.13</v>
@@ -12423,7 +12426,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B91" s="21">
         <v>-54.53</v>
@@ -12479,7 +12482,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
@@ -12513,7 +12516,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
@@ -12547,7 +12550,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
@@ -12581,7 +12584,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B95" s="15">
         <v>289.48</v>
@@ -12649,7 +12652,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
@@ -12687,7 +12690,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -12721,7 +12724,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B98" s="17">
         <v>420.07</v>
@@ -12789,7 +12792,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
@@ -12827,7 +12830,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B100" s="17">
         <v>420.07</v>
@@ -12895,7 +12898,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B101" s="17">
         <v>1211.81</v>
@@ -12963,7 +12966,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B102" s="15">
         <v>117.78</v>
@@ -13031,7 +13034,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B103" s="15">
         <v>117.78</v>
@@ -13129,7 +13132,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B105" s="15">
         <v>117.78</v>
@@ -13197,7 +13200,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B106" s="15">
         <v>117.78</v>
@@ -13265,7 +13268,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B107" s="18">
         <v>1.0</v>
@@ -14245,7 +14248,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -14618,67 +14621,67 @@
         <v>43</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -14751,7 +14754,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -14845,7 +14848,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B20" s="21">
         <v>-81.26</v>
@@ -14959,7 +14962,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B22" s="18">
         <v>41.26</v>
@@ -15093,7 +15096,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B24" s="18">
         <v>9.38</v>
@@ -15205,7 +15208,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B26" s="18">
         <v>0.94</v>
@@ -15239,7 +15242,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B27" s="21">
         <v>-0.16</v>
@@ -15295,7 +15298,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B28" s="18">
         <v>2.03</v>
@@ -15363,7 +15366,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B29" s="21">
         <v>-2.5</v>
@@ -15431,7 +15434,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B30" s="20">
         <v>0.0</v>
@@ -15477,7 +15480,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B31" s="21">
         <v>-4.22</v>
@@ -15523,7 +15526,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -15603,7 +15606,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B34" s="18">
         <v>5.63</v>
@@ -15661,7 +15664,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B35" s="21">
         <v>-10.47</v>
@@ -15729,7 +15732,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B36" s="21">
         <v>-20.32</v>
@@ -15797,7 +15800,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B37" s="18">
         <v>6.72</v>
@@ -15863,7 +15866,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B38" s="20">
         <v>0.0</v>
@@ -15911,7 +15914,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
@@ -15947,7 +15950,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
@@ -15991,7 +15994,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
@@ -16019,7 +16022,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
@@ -16057,7 +16060,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
@@ -16087,7 +16090,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
@@ -16115,7 +16118,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B45" s="23">
         <v>4.06</v>
@@ -16183,7 +16186,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B46" s="21">
         <v>-0.47</v>
@@ -16243,7 +16246,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B47" s="18">
         <v>0.16</v>
@@ -16301,7 +16304,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
@@ -16389,7 +16392,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B50" s="21">
         <v>-5.16</v>
@@ -16443,7 +16446,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
@@ -16499,7 +16502,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B52" s="20">
         <v>0.0</v>
@@ -16537,7 +16540,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B53" s="18">
         <v>10.63</v>
@@ -16581,7 +16584,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
@@ -16635,7 +16638,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B55" s="18">
         <v>0.31</v>
@@ -16669,7 +16672,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
@@ -16703,7 +16706,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
@@ -16733,7 +16736,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B58" s="21">
         <v>-5.0</v>
@@ -16765,7 +16768,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
@@ -16797,7 +16800,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
@@ -16829,7 +16832,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -16857,7 +16860,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
@@ -16885,7 +16888,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B63" s="23">
         <v>0.47</v>
@@ -16953,7 +16956,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20">
@@ -17015,7 +17018,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B65" s="21">
         <v>-6.41</v>
@@ -17081,7 +17084,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B66" s="21">
         <v>-5.94</v>
@@ -17119,7 +17122,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B67" s="21">
         <v>-26.88</v>
@@ -17171,7 +17174,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -17213,7 +17216,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
@@ -17255,7 +17258,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
@@ -17297,7 +17300,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
@@ -17329,7 +17332,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
@@ -17363,7 +17366,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
@@ -17393,7 +17396,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
@@ -17421,7 +17424,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -17449,7 +17452,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B76" s="24">
         <v>-39.23</v>
@@ -17517,7 +17520,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
@@ -17549,7 +17552,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B78" s="18">
         <v>64.43</v>
@@ -17617,7 +17620,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B79" s="18">
         <v>29.54</v>
@@ -17685,7 +17688,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
@@ -17745,7 +17748,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
@@ -17775,7 +17778,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B82" s="24">
         <v>-34.69</v>
@@ -17843,7 +17846,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
@@ -17887,7 +17890,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B84" s="20"/>
       <c r="C84" s="20"/>
@@ -18850,7 +18853,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19024,34 +19027,34 @@
         <v>38</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -19546,7 +19549,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -19648,39 +19651,39 @@
         <v>68</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AF19" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
@@ -19716,7 +19719,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B21" s="30">
         <v>960.25</v>
@@ -19812,7 +19815,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="29" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B22" s="30">
         <v>1331.55</v>
@@ -19892,7 +19895,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
@@ -19928,7 +19931,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="29" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B24" s="30">
         <v>248.03</v>
@@ -20026,7 +20029,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="29" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B25" s="30">
         <v>322.63</v>
@@ -20116,7 +20119,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B26" s="28"/>
       <c r="C26" s="28"/>
@@ -20152,7 +20155,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="29" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B27" s="32">
         <v>2.11</v>
@@ -20250,7 +20253,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="29" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B28" s="32">
         <v>2.74</v>
@@ -20340,7 +20343,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="27" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B29" s="28"/>
       <c r="C29" s="28"/>
@@ -20376,7 +20379,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="29" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B30" s="33">
         <v>1.46</v>
@@ -20472,7 +20475,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="29" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B31" s="33">
         <v>16.11</v>
@@ -20552,7 +20555,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -20588,7 +20591,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="29" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B33" s="33">
         <v>0.0</v>
@@ -20684,7 +20687,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="29" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B34" s="33">
         <v>0.0</v>
@@ -20764,7 +20767,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="29" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B35" s="33">
         <v>0.0</v>
@@ -20860,7 +20863,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B36" s="33">
         <v>0.0</v>
@@ -20940,7 +20943,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="27" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
@@ -20976,7 +20979,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B38" s="32">
         <v>0.59</v>
@@ -21072,7 +21075,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="29" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B39" s="32">
         <v>0.54</v>
@@ -21152,7 +21155,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="27" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B40" s="28"/>
       <c r="C40" s="28"/>
@@ -21188,7 +21191,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="29" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B41" s="32">
         <v>0.59</v>
@@ -21284,7 +21287,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="29" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B42" s="32">
         <v>0.54</v>
@@ -21364,7 +21367,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="27" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B43" s="28"/>
       <c r="C43" s="28"/>
@@ -21400,7 +21403,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="29" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B44" s="32">
         <v>2.24</v>
@@ -21496,7 +21499,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="29" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B45" s="32">
         <v>1.27</v>
@@ -21576,7 +21579,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="27" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B46" s="28"/>
       <c r="C46" s="28"/>
@@ -21612,7 +21615,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="29" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B47" s="32">
         <v>68.62</v>
@@ -21680,7 +21683,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="29" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" s="32">
         <v>6.21</v>
@@ -21742,7 +21745,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="27" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B49" s="28"/>
       <c r="C49" s="28"/>
@@ -21778,7 +21781,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B50" s="31"/>
       <c r="C50" s="31"/>
@@ -21848,7 +21851,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="29" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B51" s="31"/>
       <c r="C51" s="31"/>
@@ -21900,7 +21903,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="27" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B52" s="28"/>
       <c r="C52" s="28"/>
@@ -21936,7 +21939,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="29" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B53" s="31"/>
       <c r="C53" s="31"/>
@@ -22006,7 +22009,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="29" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B54" s="31"/>
       <c r="C54" s="31"/>
@@ -22056,7 +22059,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="27" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B55" s="28"/>
       <c r="C55" s="28"/>
@@ -22092,7 +22095,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="29" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B56" s="31"/>
       <c r="C56" s="32">
@@ -22166,7 +22169,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="29" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B57" s="32">
         <v>0.54</v>
@@ -22246,7 +22249,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="27" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B58" s="28"/>
       <c r="C58" s="28"/>
@@ -22282,7 +22285,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="29" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B59" s="31"/>
       <c r="C59" s="31"/>
@@ -22350,7 +22353,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="29" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B60" s="31"/>
       <c r="C60" s="31"/>
@@ -22396,7 +22399,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="27" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B61" s="28"/>
       <c r="C61" s="28"/>
@@ -22432,7 +22435,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="29" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B62" s="32">
         <v>8.68</v>
@@ -22528,7 +22531,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="29" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B63" s="32">
         <v>5.41</v>
@@ -22608,7 +22611,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="27" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B64" s="28"/>
       <c r="C64" s="28"/>
@@ -22644,7 +22647,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="29" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B65" s="32">
         <v>36.16</v>
@@ -22732,7 +22735,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="29" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B66" s="32">
         <v>20.76</v>
@@ -22810,7 +22813,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="27" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B67" s="28"/>
       <c r="C67" s="28"/>
@@ -22846,7 +22849,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="29" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B68" s="30">
         <v>235.01</v>
@@ -22914,7 +22917,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="29" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B69" s="32">
         <v>25.72</v>
@@ -22976,7 +22979,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="27" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B70" s="28"/>
       <c r="C70" s="28"/>
@@ -23012,7 +23015,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="29" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B71" s="30">
         <v>265.67</v>
@@ -23080,7 +23083,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="29" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B72" s="32">
         <v>25.8</v>
